--- a/docs/downloads/05/tbl_latrine_alaotra_analamiranga.xlsx
+++ b/docs/downloads/05/tbl_latrine_alaotra_analamiranga.xlsx
@@ -477,12 +477,6 @@
           <t>Fosse septique en commun</t>
         </is>
       </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -494,12 +488,6 @@
         <is>
           <t>Fosse septique en individuel</t>
         </is>
-      </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8">
-        <v>0.6</v>
       </c>
     </row>
   </sheetData>
